--- a/data/excel/alias.xlsx
+++ b/data/excel/alias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,12 +793,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>青年团一大</t>
+          <t>七届二中全会</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中国社会主义青年团第一次全国代表大会</t>
+          <t>中国共产党第七届中央委员会第二次全体会议</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -810,114 +810,114 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>北平</t>
+          <t>中共十八大</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>中国共产党第十八次全国代表大会</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>《论持久战》</t>
+          <t>十八大</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>论持久战</t>
+          <t>中国共产党第十八次全国代表大会</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>《中国社会各阶级的分析》</t>
+          <t>中共二十大</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>中国社会各阶级的分析</t>
+          <t>中国共产党第二十次全国代表大会</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>《星星之火</t>
+          <t>二十大</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>星星之火，可以燎原</t>
+          <t>中国共产党第二十次全国代表大会</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>可以燎原》</t>
+          <t>青年团一大</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>星星之火，可以燎原</t>
+          <t>中国社会主义青年团第一次全国代表大会</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>《实践论》</t>
+          <t>北平</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>实践论</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Location</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>《矛盾论》</t>
+          <t>《论持久战》</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>矛盾论</t>
+          <t>论持久战</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -929,15 +929,100 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>《中国社会各阶级的分析》</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>中国社会各阶级的分析</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>《星星之火</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>星星之火，可以燎原</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>可以燎原》</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>星星之火，可以燎原</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>《实践论》</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>实践论</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>《矛盾论》</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>矛盾论</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>《论联合政府》</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>论联合政府</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Document</t>
         </is>

--- a/data/excel/alias.xlsx
+++ b/data/excel/alias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,46 +589,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>八一南昌起义</t>
+          <t>全总</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>南昌起义</t>
+          <t>中华全国总工会</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>湘赣边界秋收起义</t>
+          <t>志愿军</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>秋收起义</t>
+          <t>中国人民志愿军</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>长征</t>
+          <t>八一南昌起义</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>红军长征</t>
+          <t>南昌起义</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -640,12 +640,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>二万五千里长征</t>
+          <t>湘赣边界秋收起义</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>红军长征</t>
+          <t>秋收起义</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -657,12 +657,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>双十二事变</t>
+          <t>长征</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>西安事变</t>
+          <t>红军长征</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>七七事变</t>
+          <t>二万五千里长征</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>卢沟桥事变</t>
+          <t>红军长征</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -691,41 +691,41 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>中共一大</t>
+          <t>双十二事变</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中国共产党第一次全国代表大会</t>
+          <t>西安事变</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>一大</t>
+          <t>七七事变</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中国共产党第一次全国代表大会</t>
+          <t>卢沟桥事变</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>党的一大</t>
+          <t>中共一大</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>中共七大</t>
+          <t>一大</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中国共产党第七次全国代表大会</t>
+          <t>中国共产党第一次全国代表大会</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -759,12 +759,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>七大</t>
+          <t>党的一大</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中国共产党第七次全国代表大会</t>
+          <t>中国共产党第一次全国代表大会</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -776,12 +776,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>十一届三中全会</t>
+          <t>中共七大</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>中国共产党第十一届中央委员会第三次全体会议</t>
+          <t>中国共产党第七次全国代表大会</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -793,12 +793,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>七届二中全会</t>
+          <t>七大</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中国共产党第七届中央委员会第二次全体会议</t>
+          <t>中国共产党第七次全国代表大会</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -810,12 +810,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>中共十八大</t>
+          <t>十一届三中全会</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中国共产党第十八次全国代表大会</t>
+          <t>中国共产党第十一届中央委员会第三次全体会议</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -827,12 +827,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>十八大</t>
+          <t>七届二中全会</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>中国共产党第十八次全国代表大会</t>
+          <t>中国共产党第七届中央委员会第二次全体会议</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -844,12 +844,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>中共二十大</t>
+          <t>中共十八大</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>中国共产党第二十次全国代表大会</t>
+          <t>中国共产党第十八次全国代表大会</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -861,12 +861,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>二十大</t>
+          <t>十八大</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>中国共产党第二十次全国代表大会</t>
+          <t>中国共产党第十八次全国代表大会</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -878,12 +878,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>青年团一大</t>
+          <t>中共二十大</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>中国社会主义青年团第一次全国代表大会</t>
+          <t>中国共产党第二十次全国代表大会</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -895,134 +895,712 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>北平</t>
+          <t>二十大</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>中国共产党第二十次全国代表大会</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>《论持久战》</t>
+          <t>青年团一大</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>论持久战</t>
+          <t>中国社会主义青年团第一次全国代表大会</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>《中国社会各阶级的分析》</t>
+          <t>中共二大</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>中国社会各阶级的分析</t>
+          <t>中国共产党第二次全国代表大会</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>《星星之火</t>
+          <t>二大</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>星星之火，可以燎原</t>
+          <t>中国共产党第二次全国代表大会</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>可以燎原》</t>
+          <t>中共三大</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>星星之火，可以燎原</t>
+          <t>中国共产党第三次全国代表大会</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>《实践论》</t>
+          <t>三大</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>实践论</t>
+          <t>中国共产党第三次全国代表大会</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>《矛盾论》</t>
+          <t>中共四大</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>矛盾论</t>
+          <t>中国共产党第四次全国代表大会</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>四大</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>中国共产党第四次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>中共五大</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>中国共产党第五次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>五大</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>中国共产党第五次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>中共六大</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>中国共产党第六次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>六大</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>中国共产党第六次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>中共八大</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>中国共产党第八次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>八大</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>中国共产党第八次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>中共九大</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>中国共产党第九次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>九大</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>中国共产党第九次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>中共十大</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>中国共产党第十次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>十大</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>中国共产党第十次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>中共十一大</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>中国共产党第十一次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>十一大</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>中国共产党第十一次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>中共十二大</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>中国共产党第十二次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>十二大</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>中国共产党第十二次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>中共十三大</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>中国共产党第十三次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>十三大</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>中国共产党第十三次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>中共十四大</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>中国共产党第十四次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>十四大</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>中国共产党第十四次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>中共十五大</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>中国共产党第十五次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>十五大</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>中国共产党第十五次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>中共十六大</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>中国共产党第十六次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>十六大</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>中国共产党第十六次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>中共十七大</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>中国共产党第十七次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>十七大</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>中国共产党第十七次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>中共十九大</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>中国共产党第十九次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>十九大</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>中国共产党第十九次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>北平</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>《论持久战》</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>论持久战</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>《中国社会各阶级的分析》</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>中国社会各阶级的分析</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>《星星之火</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>星星之火，可以燎原</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>可以燎原》</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>星星之火，可以燎原</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>《实践论》</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>实践论</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>《矛盾论》</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>矛盾论</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>《论联合政府》</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>论联合政府</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Document</t>
         </is>

--- a/data/excel/alias.xlsx
+++ b/data/excel/alias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,1137 +470,2633 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>中共</t>
+          <t>铁人</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中国共产党</t>
+          <t>王进喜</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>红军</t>
+          <t>诺尔曼·白求恩</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>中国工农红军</t>
+          <t>白求恩</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>国民革命军第八路军</t>
+          <t>中山先生</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>八路军</t>
+          <t>孙中山</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>十八集团军</t>
+          <t>孙文</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>八路军</t>
+          <t>孙中山</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>国民革命军陆军新编第四军</t>
+          <t>沈雁冰</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>新四军</t>
+          <t>茅盾</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>解放军</t>
+          <t>周树人</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中国人民解放军</t>
+          <t>鲁迅</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>共青团</t>
+          <t>卡尔·马克思</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中国共产主义青年团</t>
+          <t>马克思</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>全总</t>
+          <t>弗里德里希·恩格斯</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>中华全国总工会</t>
+          <t>恩格斯</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>志愿军</t>
+          <t>弗拉基米尔·列宁</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中国人民志愿军</t>
+          <t>列宁</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>八一南昌起义</t>
+          <t>约瑟夫·斯大林</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>南昌起义</t>
+          <t>斯大林</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>湘赣边界秋收起义</t>
+          <t>洛甫</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>秋收起义</t>
+          <t>张闻天</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>长征</t>
+          <t>陈绍禹</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>红军长征</t>
+          <t>王明</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>二万五千里长征</t>
+          <t>秦邦宪</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>红军长征</t>
+          <t>博古</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>双十二事变</t>
+          <t>奥托·布劳恩</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>西安事变</t>
+          <t>李德</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Person</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>七七事变</t>
+          <t>中共</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>卢沟桥事变</t>
+          <t>中国共产党</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>中共一大</t>
+          <t>红军</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中国共产党第一次全国代表大会</t>
+          <t>中国工农红军</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>一大</t>
+          <t>国民革命军第八路军</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中国共产党第一次全国代表大会</t>
+          <t>八路军</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>党的一大</t>
+          <t>十八集团军</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中国共产党第一次全国代表大会</t>
+          <t>八路军</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>中共七大</t>
+          <t>国民革命军陆军新编第四军</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>中国共产党第七次全国代表大会</t>
+          <t>新四军</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>七大</t>
+          <t>解放军</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中国共产党第七次全国代表大会</t>
+          <t>中国人民解放军</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>十一届三中全会</t>
+          <t>共青团</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中国共产党第十一届中央委员会第三次全体会议</t>
+          <t>中国共产主义青年团</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>七届二中全会</t>
+          <t>全总</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>中国共产党第七届中央委员会第二次全体会议</t>
+          <t>中华全国总工会</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>中共十八大</t>
+          <t>志愿军</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>中国共产党第十八次全国代表大会</t>
+          <t>中国人民志愿军</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>十八大</t>
+          <t>中央政治局</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>中国共产党第十八次全国代表大会</t>
+          <t>中共中央政治局</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>中共二十大</t>
+          <t>中央书记处</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>中国共产党第二十次全国代表大会</t>
+          <t>中共中央书记处</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>二十大</t>
+          <t>中央军委</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中国共产党第二十次全国代表大会</t>
+          <t>中共中央军事委员会</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>青年团一大</t>
+          <t>中央纪委</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>中国社会主义青年团第一次全国代表大会</t>
+          <t>中共中央纪律检查委员会</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>中共二大</t>
+          <t>中办</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>中国共产党第二次全国代表大会</t>
+          <t>中共中央办公厅</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>二大</t>
+          <t>中宣部</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中国共产党第二次全国代表大会</t>
+          <t>中共中央宣传部</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>中共三大</t>
+          <t>中组部</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>中国共产党第三次全国代表大会</t>
+          <t>中共中央组织部</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>三大</t>
+          <t>中央统战部</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>中国共产党第三次全国代表大会</t>
+          <t>中共中央统一战线工作部</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>中共四大</t>
+          <t>临时中央政府</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>中国共产党第四次全国代表大会</t>
+          <t>中华苏维埃共和国临时中央政府</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>四大</t>
+          <t>国务院</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>中国共产党第四次全国代表大会</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>中共五大</t>
+          <t>全国人大</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中国共产党第五次全国代表大会</t>
+          <t>全国人民代表大会</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>五大</t>
+          <t>人民政协</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中国共产党第五次全国代表大会</t>
+          <t>中国人民政治协商会议</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>中共六大</t>
+          <t>政协</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>中国共产党第六次全国代表大会</t>
+          <t>中国人民政治协商会议</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>六大</t>
+          <t>红四军</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>中国共产党第六次全国代表大会</t>
+          <t>中国工农红军第四军</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>中共八大</t>
+          <t>红一方面军</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>中国共产党第八次全国代表大会</t>
+          <t>中国工农红军第一方面军</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>八大</t>
+          <t>中央红军</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>中国共产党第八次全国代表大会</t>
+          <t>中国工农红军第一方面军</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>中共九大</t>
+          <t>红二方面军</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>中国共产党第九次全国代表大会</t>
+          <t>中国工农红军第二方面军</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>九大</t>
+          <t>红四方面军</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>中国共产党第九次全国代表大会</t>
+          <t>中国工农红军第四方面军</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>中共十大</t>
+          <t>抗联</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>中国共产党第十次全国代表大会</t>
+          <t>东北抗日联军</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>十大</t>
+          <t>一一五师</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>中国共产党第十次全国代表大会</t>
+          <t>八路军第一一五师</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>中共十一大</t>
+          <t>红二十五军</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>中国共产党第十一次全国代表大会</t>
+          <t>中国工农红军第二十五军</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>十一大</t>
+          <t>四野</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中国共产党第十一次全国代表大会</t>
+          <t>中国人民解放军第四野战军</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>中共十二大</t>
+          <t>三野</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>中国共产党第十二次全国代表大会</t>
+          <t>中国人民解放军第三野战军</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>十二大</t>
+          <t>二野</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>中国共产党第十二次全国代表大会</t>
+          <t>中国人民解放军第二野战军</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>中共十三大</t>
+          <t>一野</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>中国共产党第十三次全国代表大会</t>
+          <t>中国人民解放军第一野战军</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>十三大</t>
+          <t>全国妇联</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>中国共产党第十三次全国代表大会</t>
+          <t>中华全国妇女联合会</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>中共十四大</t>
+          <t>全国青联</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>中国共产党第十四次全国代表大会</t>
+          <t>中华全国青年联合会</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>十四大</t>
+          <t>少先队</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>中国共产党第十四次全国代表大会</t>
+          <t>中国少年先锋队</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>中共十五大</t>
+          <t>第三国际</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>中国共产党第十五次全国代表大会</t>
+          <t>共产国际</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>十五大</t>
+          <t>国民党</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>中国共产党第十五次全国代表大会</t>
+          <t>中国国民党</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>中共十六大</t>
+          <t>民盟</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>中国共产党第十六次全国代表大会</t>
+          <t>中国民主同盟</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>十六大</t>
+          <t>民革</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>中国共产党第十六次全国代表大会</t>
+          <t>中国国民党革命委员会</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>中共十七大</t>
+          <t>八一南昌起义</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>中国共产党第十七次全国代表大会</t>
+          <t>南昌起义</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>十七大</t>
+          <t>湘赣边界秋收起义</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>中国共产党第十七次全国代表大会</t>
+          <t>秋收起义</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>中共十九大</t>
+          <t>长征</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>中国共产党第十九次全国代表大会</t>
+          <t>红军长征</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>十九大</t>
+          <t>二万五千里长征</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>中国共产党第十九次全国代表大会</t>
+          <t>红军长征</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>北平</t>
+          <t>双十二事变</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>西安事变</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>《论持久战》</t>
+          <t>七七事变</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>论持久战</t>
+          <t>卢沟桥事变</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>《中国社会各阶级的分析》</t>
+          <t>中共一大</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>中国社会各阶级的分析</t>
+          <t>中国共产党第一次全国代表大会</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>《星星之火</t>
+          <t>一大</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>星星之火，可以燎原</t>
+          <t>中国共产党第一次全国代表大会</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>可以燎原》</t>
+          <t>党的一大</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>星星之火，可以燎原</t>
+          <t>中国共产党第一次全国代表大会</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>《实践论》</t>
+          <t>中共七大</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>实践论</t>
+          <t>中国共产党第七次全国代表大会</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>《矛盾论》</t>
+          <t>七大</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>矛盾论</t>
+          <t>中国共产党第七次全国代表大会</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>十一届三中全会</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>中国共产党第十一届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>七届二中全会</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>中国共产党第七届中央委员会第二次全体会议</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>中共十八大</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>中国共产党第十八次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>十八大</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>中国共产党第十八次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>中共二十大</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>中国共产党第二十次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>二十大</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>中国共产党第二十次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>青年团一大</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>中国社会主义青年团第一次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>中共二大</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>中国共产党第二次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>二大</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>中国共产党第二次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>中共三大</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>中国共产党第三次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>三大</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>中国共产党第三次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>中共四大</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>中国共产党第四次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>四大</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>中国共产党第四次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>中共五大</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>中国共产党第五次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>五大</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>中国共产党第五次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>中共六大</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>中国共产党第六次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>六大</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>中国共产党第六次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>中共八大</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>中国共产党第八次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>八大</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>中国共产党第八次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>中共九大</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>中国共产党第九次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>九大</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>中国共产党第九次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>中共十大</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>中国共产党第十次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>十大</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>中国共产党第十次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>中共十一大</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>中国共产党第十一次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>十一大</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>中国共产党第十一次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>中共十二大</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>中国共产党第十二次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>十二大</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>中国共产党第十二次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>中共十三大</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>中国共产党第十三次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>十三大</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>中国共产党第十三次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>中共十四大</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>中国共产党第十四次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>十四大</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>中国共产党第十四次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>中共十五大</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>中国共产党第十五次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>十五大</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>中国共产党第十五次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>中共十六大</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>中国共产党第十六次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>十六大</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>中国共产党第十六次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>中共十七大</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>中国共产党第十七次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>十七大</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>中国共产党第十七次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>中共十九大</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>中国共产党第十九次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>十九大</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>中国共产党第十九次全国代表大会</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>六届六中全会</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>中国共产党第六届中央委员会第六次全体会议</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>六届七中全会</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>中国共产党第六届中央委员会第七次全体会议</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>政协一届全体会议</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议第一届全体会议</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>新政协</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议第一届全体会议</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>一届全国人大一次会议</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>第一届全国人民代表大会第一次会议</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>七届三中全会</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>中国共产党第七届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>八届十一中全会</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>中国共产党第八届中央委员会第十一次全体会议</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>七千人大会</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>中央工作会议（七千人大会）</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>八届九中全会</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>中国共产党第八届中央委员会第九次全体会议</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>十一届六中全会</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>中国共产党第十一届中央委员会第六次全体会议</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>十二届三中全会</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>中国共产党第十二届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>十三届四中全会</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>中国共产党第十三届中央委员会第四次全体会议</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>十四届三中全会</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>中国共产党第十四届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>十五届五中全会</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>中国共产党第十五届中央委员会第五次全体会议</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>十六届三中全会</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>中国共产党第十六届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>十六届六中全会</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>中国共产党第十六届中央委员会第六次全体会议</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>十七届三中全会</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>中国共产党第十七届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>十七届六中全会</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>中国共产党第十七届中央委员会第六次全体会议</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>十八届三中全会</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>中国共产党第十八届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>十八届四中全会</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>中国共产党第十八届中央委员会第四次全体会议</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>十八届五中全会</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>中国共产党第十八届中央委员会第五次全体会议</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>十八届六中全会</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>中国共产党第十八届中央委员会第六次全体会议</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>十九届四中全会</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>中国共产党第十九届中央委员会第四次全体会议</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>十九届五中全会</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>中国共产党第十九届中央委员会第五次全体会议</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>十九届六中全会</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>中国共产党第十九届中央委员会第六次全体会议</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>二十届三中全会</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>中国共产党第二十届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>中共中央政治局扩大会议（庐山）</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>庐山会议</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>北平</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>嘉兴南湖</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>南湖</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>吴起镇</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>吴起</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>北京香山</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>香山</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>天安门广场</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>天安门</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>小岗</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>小岗村</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>上海浦东</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>浦东</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>雄安新区</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>雄安</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>《论持久战》</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>论持久战</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>《中国社会各阶级的分析》</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>中国社会各阶级的分析</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>《星星之火</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>星星之火，可以燎原</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>可以燎原》</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>星星之火，可以燎原</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>《实践论》</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>实践论</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>《矛盾论》</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>矛盾论</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
           <t>《论联合政府》</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>论联合政府</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>共同纲领</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议共同纲领</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>五四宪法</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>中华人民共和国宪法</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>第二个历史决议</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>关于建国以来党的若干历史问题的决议</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>第一个历史决议</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>关于若干历史问题的决议</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>第三个历史决议</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>中共中央关于党的百年奋斗重大成就和历史经验的决议</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>党章</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>中国共产党章程</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>民法典</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>中华人民共和国民法典</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>为抗日救国告全体同胞书</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>八一宣言</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
         <is>
           <t>Document</t>
         </is>

--- a/data/excel/alias.xlsx
+++ b/data/excel/alias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C158"/>
+  <dimension ref="A1:C161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1201,12 +1201,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>红二十五军</t>
+          <t>一二〇师</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>中国工农红军第二十五军</t>
+          <t>八路军第一二〇师</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1218,12 +1218,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>四野</t>
+          <t>一二九师</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中国人民解放军第四野战军</t>
+          <t>八路军第一二九师</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1235,12 +1235,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>三野</t>
+          <t>社会主义青年团</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>中国人民解放军第三野战军</t>
+          <t>中国社会主义青年团</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>二野</t>
+          <t>红二十五军</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>中国人民解放军第二野战军</t>
+          <t>中国工农红军第二十五军</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1269,12 +1269,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>一野</t>
+          <t>四野</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>中国人民解放军第一野战军</t>
+          <t>中国人民解放军第四野战军</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1286,12 +1286,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>全国妇联</t>
+          <t>三野</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>中华全国妇女联合会</t>
+          <t>中国人民解放军第三野战军</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1303,12 +1303,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>全国青联</t>
+          <t>二野</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>中华全国青年联合会</t>
+          <t>中国人民解放军第二野战军</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1320,12 +1320,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>少先队</t>
+          <t>一野</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>中国少年先锋队</t>
+          <t>中国人民解放军第一野战军</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1337,12 +1337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>第三国际</t>
+          <t>全国妇联</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>共产国际</t>
+          <t>中华全国妇女联合会</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1354,12 +1354,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>国民党</t>
+          <t>全国青联</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>中国国民党</t>
+          <t>中华全国青年联合会</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>民盟</t>
+          <t>少先队</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>中国民主同盟</t>
+          <t>中国少年先锋队</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1388,12 +1388,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>民革</t>
+          <t>第三国际</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>中国国民党革命委员会</t>
+          <t>共产国际</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1405,63 +1405,63 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>八一南昌起义</t>
+          <t>国民党</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>南昌起义</t>
+          <t>中国国民党</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>湘赣边界秋收起义</t>
+          <t>民盟</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>秋收起义</t>
+          <t>中国民主同盟</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>长征</t>
+          <t>民革</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>红军长征</t>
+          <t>中国国民党革命委员会</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>二万五千里长征</t>
+          <t>八一南昌起义</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>红军长征</t>
+          <t>南昌起义</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1473,12 +1473,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>双十二事变</t>
+          <t>湘赣边界秋收起义</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>西安事变</t>
+          <t>秋收起义</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1490,12 +1490,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>七七事变</t>
+          <t>长征</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>卢沟桥事变</t>
+          <t>红军长征</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1507,63 +1507,63 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>中共一大</t>
+          <t>二万五千里长征</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>中国共产党第一次全国代表大会</t>
+          <t>红军长征</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>一大</t>
+          <t>双十二事变</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>中国共产党第一次全国代表大会</t>
+          <t>西安事变</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>党的一大</t>
+          <t>七七事变</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>中国共产党第一次全国代表大会</t>
+          <t>卢沟桥事变</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>中共七大</t>
+          <t>中共一大</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>中国共产党第七次全国代表大会</t>
+          <t>中国共产党第一次全国代表大会</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1575,12 +1575,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>七大</t>
+          <t>一大</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>中国共产党第七次全国代表大会</t>
+          <t>中国共产党第一次全国代表大会</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1592,12 +1592,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>十一届三中全会</t>
+          <t>党的一大</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>中国共产党第十一届中央委员会第三次全体会议</t>
+          <t>中国共产党第一次全国代表大会</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>七届二中全会</t>
+          <t>中共七大</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>中国共产党第七届中央委员会第二次全体会议</t>
+          <t>中国共产党第七次全国代表大会</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1626,12 +1626,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>中共十八大</t>
+          <t>七大</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>中国共产党第十八次全国代表大会</t>
+          <t>中国共产党第七次全国代表大会</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1643,12 +1643,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>十八大</t>
+          <t>十一届三中全会</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>中国共产党第十八次全国代表大会</t>
+          <t>中国共产党第十一届中央委员会第三次全体会议</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1660,12 +1660,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>中共二十大</t>
+          <t>七届二中全会</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>中国共产党第二十次全国代表大会</t>
+          <t>中国共产党第七届中央委员会第二次全体会议</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1677,12 +1677,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>二十大</t>
+          <t>中共十八大</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>中国共产党第二十次全国代表大会</t>
+          <t>中国共产党第十八次全国代表大会</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1694,12 +1694,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>青年团一大</t>
+          <t>十八大</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>中国社会主义青年团第一次全国代表大会</t>
+          <t>中国共产党第十八次全国代表大会</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1711,12 +1711,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>中共二大</t>
+          <t>中共二十大</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>中国共产党第二次全国代表大会</t>
+          <t>中国共产党第二十次全国代表大会</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1728,12 +1728,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>二大</t>
+          <t>二十大</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>中国共产党第二次全国代表大会</t>
+          <t>中国共产党第二十次全国代表大会</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1745,12 +1745,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>中共三大</t>
+          <t>青年团一大</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>中国共产党第三次全国代表大会</t>
+          <t>中国社会主义青年团第一次全国代表大会</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1762,12 +1762,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>三大</t>
+          <t>中共二大</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>中国共产党第三次全国代表大会</t>
+          <t>中国共产党第二次全国代表大会</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1779,12 +1779,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>中共四大</t>
+          <t>二大</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>中国共产党第四次全国代表大会</t>
+          <t>中国共产党第二次全国代表大会</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1796,12 +1796,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>四大</t>
+          <t>中共三大</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>中国共产党第四次全国代表大会</t>
+          <t>中国共产党第三次全国代表大会</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1813,12 +1813,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>中共五大</t>
+          <t>三大</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>中国共产党第五次全国代表大会</t>
+          <t>中国共产党第三次全国代表大会</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1830,12 +1830,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>五大</t>
+          <t>中共四大</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>中国共产党第五次全国代表大会</t>
+          <t>中国共产党第四次全国代表大会</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1847,12 +1847,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>中共六大</t>
+          <t>四大</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>中国共产党第六次全国代表大会</t>
+          <t>中国共产党第四次全国代表大会</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1864,12 +1864,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>六大</t>
+          <t>中共五大</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>中国共产党第六次全国代表大会</t>
+          <t>中国共产党第五次全国代表大会</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>中共八大</t>
+          <t>五大</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>中国共产党第八次全国代表大会</t>
+          <t>中国共产党第五次全国代表大会</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1898,12 +1898,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>八大</t>
+          <t>中共六大</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>中国共产党第八次全国代表大会</t>
+          <t>中国共产党第六次全国代表大会</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1915,12 +1915,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>中共九大</t>
+          <t>六大</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>中国共产党第九次全国代表大会</t>
+          <t>中国共产党第六次全国代表大会</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1932,12 +1932,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>九大</t>
+          <t>中共八大</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>中国共产党第九次全国代表大会</t>
+          <t>中国共产党第八次全国代表大会</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1949,12 +1949,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>中共十大</t>
+          <t>八大</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>中国共产党第十次全国代表大会</t>
+          <t>中国共产党第八次全国代表大会</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -1966,12 +1966,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>十大</t>
+          <t>中共九大</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>中国共产党第十次全国代表大会</t>
+          <t>中国共产党第九次全国代表大会</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -1983,12 +1983,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>中共十一大</t>
+          <t>九大</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>中国共产党第十一次全国代表大会</t>
+          <t>中国共产党第九次全国代表大会</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2000,12 +2000,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>十一大</t>
+          <t>中共十大</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>中国共产党第十一次全国代表大会</t>
+          <t>中国共产党第十次全国代表大会</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2017,12 +2017,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>中共十二大</t>
+          <t>十大</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>中国共产党第十二次全国代表大会</t>
+          <t>中国共产党第十次全国代表大会</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2034,12 +2034,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>十二大</t>
+          <t>中共十一大</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>中国共产党第十二次全国代表大会</t>
+          <t>中国共产党第十一次全国代表大会</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>中共十三大</t>
+          <t>十一大</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>中国共产党第十三次全国代表大会</t>
+          <t>中国共产党第十一次全国代表大会</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2068,12 +2068,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>十三大</t>
+          <t>中共十二大</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>中国共产党第十三次全国代表大会</t>
+          <t>中国共产党第十二次全国代表大会</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2085,12 +2085,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>中共十四大</t>
+          <t>十二大</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>中国共产党第十四次全国代表大会</t>
+          <t>中国共产党第十二次全国代表大会</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2102,12 +2102,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>十四大</t>
+          <t>中共十三大</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>中国共产党第十四次全国代表大会</t>
+          <t>中国共产党第十三次全国代表大会</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2119,12 +2119,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>中共十五大</t>
+          <t>十三大</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>中国共产党第十五次全国代表大会</t>
+          <t>中国共产党第十三次全国代表大会</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2136,12 +2136,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>十五大</t>
+          <t>中共十四大</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>中国共产党第十五次全国代表大会</t>
+          <t>中国共产党第十四次全国代表大会</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2153,12 +2153,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>中共十六大</t>
+          <t>十四大</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>中国共产党第十六次全国代表大会</t>
+          <t>中国共产党第十四次全国代表大会</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2170,12 +2170,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>十六大</t>
+          <t>中共十五大</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>中国共产党第十六次全国代表大会</t>
+          <t>中国共产党第十五次全国代表大会</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2187,12 +2187,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>中共十七大</t>
+          <t>十五大</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>中国共产党第十七次全国代表大会</t>
+          <t>中国共产党第十五次全国代表大会</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2204,12 +2204,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>十七大</t>
+          <t>中共十六大</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>中国共产党第十七次全国代表大会</t>
+          <t>中国共产党第十六次全国代表大会</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2221,12 +2221,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>中共十九大</t>
+          <t>十六大</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>中国共产党第十九次全国代表大会</t>
+          <t>中国共产党第十六次全国代表大会</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>十九大</t>
+          <t>中共十七大</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>中国共产党第十九次全国代表大会</t>
+          <t>中国共产党第十七次全国代表大会</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2255,12 +2255,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>六届六中全会</t>
+          <t>十七大</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>中国共产党第六届中央委员会第六次全体会议</t>
+          <t>中国共产党第十七次全国代表大会</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2272,12 +2272,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>六届七中全会</t>
+          <t>中共十九大</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>中国共产党第六届中央委员会第七次全体会议</t>
+          <t>中国共产党第十九次全国代表大会</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2289,12 +2289,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>政协一届全体会议</t>
+          <t>十九大</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议第一届全体会议</t>
+          <t>中国共产党第十九次全国代表大会</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2306,12 +2306,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>新政协</t>
+          <t>六届六中全会</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议第一届全体会议</t>
+          <t>中国共产党第六届中央委员会第六次全体会议</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2323,12 +2323,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>一届全国人大一次会议</t>
+          <t>六届七中全会</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>第一届全国人民代表大会第一次会议</t>
+          <t>中国共产党第六届中央委员会第七次全体会议</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2340,12 +2340,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>七届三中全会</t>
+          <t>政协一届全体会议</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>中国共产党第七届中央委员会第三次全体会议</t>
+          <t>中国人民政治协商会议第一届全体会议</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2357,12 +2357,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>八届十一中全会</t>
+          <t>新政协</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>中国共产党第八届中央委员会第十一次全体会议</t>
+          <t>中国人民政治协商会议第一届全体会议</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2374,12 +2374,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>七千人大会</t>
+          <t>一届全国人大一次会议</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>中央工作会议（七千人大会）</t>
+          <t>第一届全国人民代表大会第一次会议</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2391,12 +2391,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>八届九中全会</t>
+          <t>七届三中全会</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>中国共产党第八届中央委员会第九次全体会议</t>
+          <t>中国共产党第七届中央委员会第三次全体会议</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2408,12 +2408,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>十一届六中全会</t>
+          <t>八届十一中全会</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>中国共产党第十一届中央委员会第六次全体会议</t>
+          <t>中国共产党第八届中央委员会第十一次全体会议</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>十二届三中全会</t>
+          <t>七千人大会</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>中国共产党第十二届中央委员会第三次全体会议</t>
+          <t>中央工作会议（七千人大会）</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2442,12 +2442,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>十三届四中全会</t>
+          <t>八届九中全会</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>中国共产党第十三届中央委员会第四次全体会议</t>
+          <t>中国共产党第八届中央委员会第九次全体会议</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2459,12 +2459,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>十四届三中全会</t>
+          <t>十一届六中全会</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>中国共产党第十四届中央委员会第三次全体会议</t>
+          <t>中国共产党第十一届中央委员会第六次全体会议</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2476,12 +2476,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>十五届五中全会</t>
+          <t>十二届三中全会</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>中国共产党第十五届中央委员会第五次全体会议</t>
+          <t>中国共产党第十二届中央委员会第三次全体会议</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2493,12 +2493,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>十六届三中全会</t>
+          <t>十三届四中全会</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>中国共产党第十六届中央委员会第三次全体会议</t>
+          <t>中国共产党第十三届中央委员会第四次全体会议</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2510,12 +2510,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>十六届六中全会</t>
+          <t>十四届三中全会</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>中国共产党第十六届中央委员会第六次全体会议</t>
+          <t>中国共产党第十四届中央委员会第三次全体会议</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2527,12 +2527,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>十七届三中全会</t>
+          <t>十五届五中全会</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>中国共产党第十七届中央委员会第三次全体会议</t>
+          <t>中国共产党第十五届中央委员会第五次全体会议</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2544,12 +2544,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>十七届六中全会</t>
+          <t>十六届三中全会</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>中国共产党第十七届中央委员会第六次全体会议</t>
+          <t>中国共产党第十六届中央委员会第三次全体会议</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>十八届三中全会</t>
+          <t>十六届六中全会</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>中国共产党第十八届中央委员会第三次全体会议</t>
+          <t>中国共产党第十六届中央委员会第六次全体会议</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2578,12 +2578,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>十八届四中全会</t>
+          <t>十七届三中全会</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>中国共产党第十八届中央委员会第四次全体会议</t>
+          <t>中国共产党第十七届中央委员会第三次全体会议</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2595,12 +2595,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>十八届五中全会</t>
+          <t>十七届六中全会</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>中国共产党第十八届中央委员会第五次全体会议</t>
+          <t>中国共产党第十七届中央委员会第六次全体会议</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2612,12 +2612,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>十八届六中全会</t>
+          <t>十八届三中全会</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>中国共产党第十八届中央委员会第六次全体会议</t>
+          <t>中国共产党第十八届中央委员会第三次全体会议</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2629,12 +2629,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>十九届四中全会</t>
+          <t>十八届四中全会</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>中国共产党第十九届中央委员会第四次全体会议</t>
+          <t>中国共产党第十八届中央委员会第四次全体会议</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2646,12 +2646,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>十九届五中全会</t>
+          <t>十八届五中全会</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>中国共产党第十九届中央委员会第五次全体会议</t>
+          <t>中国共产党第十八届中央委员会第五次全体会议</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2663,12 +2663,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>十九届六中全会</t>
+          <t>十八届六中全会</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>中国共产党第十九届中央委员会第六次全体会议</t>
+          <t>中国共产党第十八届中央委员会第六次全体会议</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>二十届三中全会</t>
+          <t>十九届四中全会</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>中国共产党第二十届中央委员会第三次全体会议</t>
+          <t>中国共产党第十九届中央委员会第四次全体会议</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>中共中央政治局扩大会议（庐山）</t>
+          <t>十九届五中全会</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>庐山会议</t>
+          <t>中国共产党第十九届中央委员会第五次全体会议</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -2714,63 +2714,63 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>北平</t>
+          <t>十九届六中全会</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>中国共产党第十九届中央委员会第六次全体会议</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>嘉兴南湖</t>
+          <t>二十届三中全会</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>南湖</t>
+          <t>中国共产党第二十届中央委员会第三次全体会议</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>吴起镇</t>
+          <t>中共中央政治局扩大会议（庐山）</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>吴起</t>
+          <t>庐山会议</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>北京香山</t>
+          <t>北平</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>香山</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2782,12 +2782,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>天安门广场</t>
+          <t>嘉兴南湖</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>天安门</t>
+          <t>南湖</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>小岗</t>
+          <t>吴起镇</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>小岗村</t>
+          <t>吴起</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -2816,12 +2816,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>上海浦东</t>
+          <t>北京香山</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>浦东</t>
+          <t>香山</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -2833,12 +2833,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>雄安新区</t>
+          <t>天安门广场</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>雄安</t>
+          <t>天安门</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -2850,63 +2850,63 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>《论持久战》</t>
+          <t>小岗</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>论持久战</t>
+          <t>小岗村</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Location</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>《中国社会各阶级的分析》</t>
+          <t>上海浦东</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>中国社会各阶级的分析</t>
+          <t>浦东</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Location</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>《星星之火</t>
+          <t>雄安新区</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>星星之火，可以燎原</t>
+          <t>雄安</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Location</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>可以燎原》</t>
+          <t>《论持久战》</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>星星之火，可以燎原</t>
+          <t>论持久战</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -2918,12 +2918,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>《实践论》</t>
+          <t>《中国社会各阶级的分析》</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>实践论</t>
+          <t>中国社会各阶级的分析</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -2935,12 +2935,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>《矛盾论》</t>
+          <t>《星星之火</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>矛盾论</t>
+          <t>星星之火，可以燎原</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -2952,12 +2952,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>《论联合政府》</t>
+          <t>可以燎原》</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>论联合政府</t>
+          <t>星星之火，可以燎原</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -2969,12 +2969,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>共同纲领</t>
+          <t>《实践论》</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>中国人民政治协商会议共同纲领</t>
+          <t>实践论</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -2986,12 +2986,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>五四宪法</t>
+          <t>《矛盾论》</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>中华人民共和国宪法</t>
+          <t>矛盾论</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3003,12 +3003,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>第二个历史决议</t>
+          <t>《论联合政府》</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>关于建国以来党的若干历史问题的决议</t>
+          <t>论联合政府</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3020,12 +3020,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>第一个历史决议</t>
+          <t>共同纲领</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>关于若干历史问题的决议</t>
+          <t>中国人民政治协商会议共同纲领</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3037,12 +3037,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>第三个历史决议</t>
+          <t>五四宪法</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>中共中央关于党的百年奋斗重大成就和历史经验的决议</t>
+          <t>中华人民共和国宪法</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3054,12 +3054,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>党章</t>
+          <t>第二个历史决议</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>中国共产党章程</t>
+          <t>关于建国以来党的若干历史问题的决议</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3071,12 +3071,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>民法典</t>
+          <t>第一个历史决议</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>中华人民共和国民法典</t>
+          <t>关于若干历史问题的决议</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3088,15 +3088,66 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
+          <t>第三个历史决议</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>中共中央关于党的百年奋斗重大成就和历史经验的决议</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>党章</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>中国共产党章程</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>民法典</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>中华人民共和国民法典</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
           <t>为抗日救国告全体同胞书</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>八一宣言</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
